--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484792_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484792_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0583</v>
+        <v>3.8571</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1246</v>
+        <v>1.9499</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9337</v>
+        <v>1.9072</v>
       </c>
       <c r="G2" t="n">
         <v>4.9245</v>
@@ -610,13 +610,13 @@
         <v>1.5096</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8094</v>
+        <v>-1.0106</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6183</v>
+        <v>0.4436</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.4278</v>
+        <v>-1.4542</v>
       </c>
       <c r="V2" t="n">
         <v>1.2642</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. CAMEROS JUAN</t>
+          <t>Á. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8263</v>
+        <v>0.6339</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.0206</v>
+        <v>0.6339</v>
       </c>
       <c r="F3" t="n">
-        <v>1.847</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7549</v>
+        <v>0.6339</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.9025</v>
+        <v>0.6339</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1476</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.8288</v>
+        <v>0.6339</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8288</v>
+        <v>0.6339</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07389999999999999</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0737</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1476</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.5096</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1474</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.035</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1124</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9434</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Á. PINTO MEDINA</t>
+          <t>J. ARTIGUES DAÑOBEITIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DAÑOBEITIA</t>
+          <t>A. DOMINGUEZ CARRAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6339</v>
+        <v>0.0579</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6339</v>
+        <v>-2.1871</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2.245</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6339</v>
+        <v>0.2276</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6339</v>
+        <v>0.6519</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0.4243</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6339</v>
+        <v>-2.7158</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6339</v>
+        <v>-0.7756</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.9402</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.9433</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.4275</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.5158</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1.5094</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-1.7364</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.9624</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2828</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ CARRAL</t>
+          <t>C. SANCHEZ VIDAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2553</v>
+        <v>-0.0852</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1484</v>
+        <v>1.5181</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4037</v>
+        <v>-1.6033</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2276</v>
+        <v>2.1829</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6519</v>
+        <v>1.0784</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4243</v>
+        <v>1.1045</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.7158</v>
+        <v>1.1942</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7756</v>
+        <v>1.1942</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9402</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9433</v>
+        <v>0.9887</v>
       </c>
       <c r="N6" t="n">
-        <v>1.4275</v>
+        <v>-0.1158</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5158</v>
+        <v>1.1045</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3774</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3209</v>
+        <v>1.1322</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.312</v>
+        <v>-0.532</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2656</v>
+        <v>0.7018</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.5777</v>
+        <v>-1.2338</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9624</v>
+        <v>-0.9813</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2452</v>
+        <v>1.5091</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2828</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. SANCHEZ VIDAL</t>
+          <t>I. HORRACH SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1399</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.849</v>
+        <v>-1.6556</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7091</v>
+        <v>1.0734</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1829</v>
+        <v>0.8645</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0784</v>
+        <v>-0.3459</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1045</v>
+        <v>1.2103</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1942</v>
+        <v>0.1679</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1942</v>
+        <v>0.1268</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9887</v>
+        <v>0.6965</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1158</v>
+        <v>-0.4727</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1045</v>
+        <v>1.1692</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R7" t="n">
         <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3069</v>
+        <v>-0.9938</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0328</v>
+        <v>-0.2384</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.3396</v>
+        <v>-0.7553</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9813</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5091</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.6137</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.9242</v>
+        <v>-3.4757</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9943</v>
+        <v>2.862</v>
       </c>
       <c r="G8" t="n">
         <v>1.8277</v>
@@ -1078,13 +1078,13 @@
         <v>1.6983</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.5688</v>
+        <v>-2.2526</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9624</v>
+        <v>-0.5139</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.6065</v>
+        <v>-1.7387</v>
       </c>
       <c r="V8" t="n">
         <v>0.9434</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. HORRACH SANCHEZ</t>
+          <t>D. CAMEROS JUAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.7131999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8505</v>
+        <v>-2.1898</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8882</v>
+        <v>1.4766</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8645</v>
+        <v>-0.7549</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3459</v>
+        <v>-1.9025</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2103</v>
+        <v>1.1476</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1679</v>
+        <v>-0.8288</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1268</v>
+        <v>-0.8288</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0411</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6965</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4727</v>
+        <v>-1.0737</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1692</v>
+        <v>1.1476</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1887</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1322</v>
+        <v>1.3209</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3738</v>
+        <v>0.6078</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4333</v>
+        <v>0.8658</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9405</v>
+        <v>-0.258</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.9434</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.6036</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. ALEMANY GARCIA</t>
+          <t>J. ARTIGUES DANOBEITIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4729</v>
+        <v>-1.9297</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3056</v>
+        <v>-4.1974</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1673</v>
+        <v>2.2676</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0515</v>
+        <v>0.5745</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6402</v>
+        <v>-0.1377</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4113</v>
+        <v>0.7123</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2569</v>
+        <v>-1.0697</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6073</v>
+        <v>-1.0456</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6496</v>
+        <v>-0.0241</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2054</v>
+        <v>1.6442</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0329</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2383</v>
+        <v>0.7363</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7548</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6666</v>
+        <v>-1.6362</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1052</v>
+        <v>-0.2972</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5614</v>
+        <v>-1.339</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DANOBEITIA</t>
+          <t>F. ALEMANY GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6789</v>
+        <v>-1.9509</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8407</v>
+        <v>-1.9159</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1618</v>
+        <v>-0.035</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5745</v>
+        <v>-1.0515</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1377</v>
+        <v>-0.6402</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7123</v>
+        <v>-0.4113</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0697</v>
+        <v>-1.2569</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0456</v>
+        <v>-0.6073</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0241</v>
+        <v>-0.6496</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6442</v>
+        <v>0.2054</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9078000000000001</v>
+        <v>-0.0329</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7363</v>
+        <v>0.2383</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5096</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3209</v>
+        <v>0.1887</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3854</v>
+        <v>-0.1446</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9406</v>
+        <v>0.2845</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4448</v>
+        <v>-0.4291</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.748</v>
+        <v>-2.966</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7613</v>
+        <v>-1.7411</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9868</v>
+        <v>-1.2249</v>
       </c>
       <c r="G12" t="n">
         <v>2.367</v>
@@ -1390,13 +1390,13 @@
         <v>0.9435</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0587</v>
+        <v>-1.2766</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0436</v>
+        <v>-0.0234</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0151</v>
+        <v>-1.2532</v>
       </c>
       <c r="V12" t="n">
         <v>-4.0564</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2386</v>
+        <v>-5.237</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.6629</v>
+        <v>-6.0582</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4244</v>
+        <v>0.8212</v>
       </c>
       <c r="G13" t="n">
         <v>-4.0372</v>
@@ -1468,13 +1468,13 @@
         <v>1.6983</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3526</v>
+        <v>-1.351</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4181</v>
+        <v>0.1867</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9345</v>
+        <v>-1.5377</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6036</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.482900000000001</v>
+        <v>-8.895100000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.2728</v>
+        <v>-18.685</v>
       </c>
       <c r="F14" t="n">
-        <v>9.789899999999999</v>
+        <v>9.7898</v>
       </c>
       <c r="G14" t="n">
         <v>8.392899999999999</v>
@@ -1522,7 +1522,7 @@
         <v>-5.3943</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3439999999999999</v>
+        <v>0.3439999999999994</v>
       </c>
       <c r="L14" t="n">
         <v>-5.7384</v>
@@ -1546,13 +1546,13 @@
         <v>12.2655</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.6868</v>
+        <v>-10.099</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0485</v>
+        <v>1.6365</v>
       </c>
       <c r="U14" t="n">
-        <v>-11.7355</v>
+        <v>-11.7354</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5279</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0251</v>
+        <v>6.3575</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6324</v>
+        <v>3.3658</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3927</v>
+        <v>2.9917</v>
       </c>
       <c r="G15" t="n">
         <v>1.1202</v>
@@ -1624,13 +1624,13 @@
         <v>2.6418</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9233</v>
+        <v>2.2557</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3958</v>
+        <v>2.1292</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4725</v>
+        <v>0.1265</v>
       </c>
       <c r="V15" t="n">
         <v>0.3398</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2492</v>
+        <v>3.5852</v>
       </c>
       <c r="E16" t="n">
-        <v>0.492</v>
+        <v>-0.0926</v>
       </c>
       <c r="F16" t="n">
-        <v>3.7572</v>
+        <v>3.6778</v>
       </c>
       <c r="G16" t="n">
         <v>0.6843</v>
@@ -1702,13 +1702,13 @@
         <v>1.887</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3196</v>
+        <v>1.6557</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9175</v>
+        <v>1.3329</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4022</v>
+        <v>0.3228</v>
       </c>
       <c r="V16" t="n">
         <v>0.3018</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5918</v>
+        <v>2.5441</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0056</v>
+        <v>0.5441</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5862</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>1.9112</v>
@@ -1780,13 +1780,13 @@
         <v>2.4531</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3413</v>
+        <v>2.2936</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5722</v>
+        <v>2.1107</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2309</v>
+        <v>0.1829</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3398</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>P. LOPEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6611</v>
+        <v>2.3935</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6896</v>
+        <v>0.1414</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3507</v>
+        <v>2.2521</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4342</v>
+        <v>-0.8115</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1135</v>
+        <v>-1.8352</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3207</v>
+        <v>1.0237</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.4332</v>
+        <v>-1.1824</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4845</v>
+        <v>-1.1669</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9487</v>
+        <v>-0.0156</v>
       </c>
       <c r="M18" t="n">
-        <v>0.999</v>
+        <v>0.371</v>
       </c>
       <c r="N18" t="n">
-        <v>0.371</v>
+        <v>-0.6683</v>
       </c>
       <c r="O18" t="n">
-        <v>0.628</v>
+        <v>1.0393</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1887</v>
+        <v>1.6983</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0757</v>
+        <v>2.6418</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9445</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6875</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.257</v>
+        <v>-0.1381</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.038</v>
+        <v>0.9244</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0569</v>
+        <v>1.547</v>
       </c>
       <c r="X18" t="n">
-        <v>0.019</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. LOPEZ DOMINGUEZ</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.719</v>
+        <v>1.1548</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6124</v>
+        <v>-2.3716</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3315</v>
+        <v>3.5264</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8115</v>
+        <v>-1.4342</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8352</v>
+        <v>-0.1135</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0237</v>
+        <v>-1.3207</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1824</v>
+        <v>-2.4332</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1669</v>
+        <v>-0.4845</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0156</v>
+        <v>-1.9487</v>
       </c>
       <c r="M19" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="N19" t="n">
         <v>0.371</v>
       </c>
-      <c r="N19" t="n">
-        <v>-0.6683</v>
-      </c>
       <c r="O19" t="n">
-        <v>1.0393</v>
+        <v>0.628</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6983</v>
+        <v>0.1887</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6418</v>
+        <v>2.0757</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0922</v>
+        <v>2.4382</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0335</v>
+        <v>2.0055</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0587</v>
+        <v>0.4328</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9244</v>
+        <v>-0.038</v>
       </c>
       <c r="W19" t="n">
-        <v>1.547</v>
+        <v>-0.0569</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6226</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4404</v>
+        <v>0.3249</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1141</v>
+        <v>-0.309</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5545</v>
+        <v>0.6339</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7106</v>
@@ -2014,13 +2014,13 @@
         <v>0.5661</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5849</v>
+        <v>0.4694</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4979</v>
+        <v>0.303</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.1664</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1177</v>
+        <v>0.2354</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4915</v>
+        <v>-3.047</v>
       </c>
       <c r="F22" t="n">
-        <v>3.3738</v>
+        <v>3.2824</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6219</v>
+        <v>-4.0519</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6951</v>
+        <v>-1.1567</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.317</v>
+        <v>-2.8952</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.6209</v>
+        <v>-4.6783</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1942</v>
+        <v>-1.415</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.8151</v>
+        <v>-3.2634</v>
       </c>
       <c r="M22" t="n">
-        <v>0.999</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5009</v>
+        <v>0.2583</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4981</v>
+        <v>0.3682</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9435</v>
+        <v>2.0757</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4391</v>
+        <v>2.2116</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2664</v>
+        <v>1.6313</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1727</v>
+        <v>0.5803</v>
       </c>
       <c r="V22" t="n">
-        <v>1.8868</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2262</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5965</v>
+        <v>0.2092</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1188</v>
+        <v>-3.4197</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5223</v>
+        <v>3.6289</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.0519</v>
+        <v>-1.6219</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1567</v>
+        <v>1.6951</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.8952</v>
+        <v>-3.317</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.6783</v>
+        <v>-2.6209</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.415</v>
+        <v>1.1942</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.2634</v>
+        <v>-3.8151</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.999</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2583</v>
+        <v>0.5009</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3682</v>
+        <v>0.4981</v>
       </c>
       <c r="P23" t="n">
-        <v>2.0757</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0757</v>
+        <v>1.887</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3797</v>
+        <v>0.8878</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5596</v>
+        <v>0.8054</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1798</v>
+        <v>0.0824</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.8868</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.6606</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8435</v>
+        <v>-1.6402</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1546</v>
+        <v>-2.0571</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3111</v>
+        <v>0.4169</v>
       </c>
       <c r="G24" t="n">
         <v>-1.4314</v>
@@ -2326,13 +2326,13 @@
         <v>0.5661</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0347</v>
+        <v>0.1686</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0247</v>
+        <v>0.1221</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0594</v>
+        <v>0.0465</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.963</v>
+        <v>-3.4001</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0558</v>
+        <v>-2.8609</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9072</v>
+        <v>-0.5392</v>
       </c>
       <c r="G25" t="n">
         <v>-2.3642</v>
@@ -2404,13 +2404,13 @@
         <v>1.1322</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2404</v>
+        <v>0.3224</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3803</v>
+        <v>0.5752</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6207</v>
+        <v>-0.2527</v>
       </c>
       <c r="V25" t="n">
         <v>-1.547</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>9.482899999999997</v>
+        <v>12.0813</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.7898</v>
+        <v>-9.7896</v>
       </c>
       <c r="F26" t="n">
-        <v>19.2728</v>
+        <v>21.8709</v>
       </c>
       <c r="G26" t="n">
         <v>-8.392999999999999</v>
@@ -2452,7 +2452,7 @@
         <v>-2.113</v>
       </c>
       <c r="I26" t="n">
-        <v>-6.279999999999999</v>
+        <v>-6.280000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>-13.787</v>
@@ -2482,22 +2482,22 @@
         <v>17.9265</v>
       </c>
       <c r="S26" t="n">
-        <v>10.6869</v>
+        <v>13.2852</v>
       </c>
       <c r="T26" t="n">
         <v>11.7356</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0485</v>
+        <v>1.5498</v>
       </c>
       <c r="V26" t="n">
         <v>1.528</v>
       </c>
       <c r="W26" t="n">
-        <v>4.527100000000001</v>
+        <v>4.5271</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.999000000000001</v>
+        <v>-2.999</v>
       </c>
     </row>
   </sheetData>
